--- a/diseases/d053/2015-2019.xlsx
+++ b/diseases/d053/2015-2019.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2247,6 +2257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2984,6 +2999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3869,6 +3889,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4606,6 +4631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5343,6 +5373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6228,6 +6263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6965,6 +7005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7702,6 +7747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8587,6 +8637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9324,6 +9379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10209,6 +10269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10946,6 +11011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11683,6 +11753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12568,6 +12643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13305,6 +13385,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14042,6 +14127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14927,6 +15017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15664,6 +15759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16401,6 +16501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17286,6 +17391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18023,6 +18133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18760,6 +18875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19645,6 +19765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20382,6 +20507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21119,6 +21249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22004,6 +22139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22741,6 +22881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23478,6 +23623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24363,6 +24513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25100,6 +25255,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25985,6 +26145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26722,6 +26887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27459,6 +27629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28344,6 +28519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29081,6 +29261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29818,6 +30003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30555,6 +30745,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31440,6 +31635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32177,6 +32377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33062,6 +33267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33799,6 +34009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34536,6 +34751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35421,6 +35641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36158,6 +36383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36895,6 +37125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37780,6 +38015,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38517,6 +38757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39402,6 +39647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40139,6 +40389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40876,6 +41131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41613,6 +41873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42498,6 +42763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43235,6 +43505,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43972,6 +44247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44857,6 +45137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45594,6 +45879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46479,6 +46769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47214,6 +47509,11 @@
       <c r="S317" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
